--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BE7221-E73F-4CDF-9B74-BBE2C3964C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1F630C-414B-4B90-A9A1-EB77B83DED3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2366,48 +2366,96 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46212</v>
+      </c>
+      <c r="B34" s="14">
+        <v>570</v>
+      </c>
+      <c r="C34" s="14">
+        <v>50</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>90</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>120</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46243</v>
+      </c>
+      <c r="B35" s="14">
+        <v>540</v>
+      </c>
+      <c r="C35" s="14">
+        <v>50</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>90</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>120</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1F630C-414B-4B90-A9A1-EB77B83DED3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011C7138-2E4C-40AC-A5E2-557ED1C0C450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>Today is my dbms practical exam of ca and my exam gone good.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excited because today was celebrated fresher party in lpu , so I was enjoy very much. </t>
   </si>
 </sst>
 </file>
@@ -2458,48 +2461,96 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B36" s="14">
+        <v>450</v>
+      </c>
+      <c r="C36" s="14">
+        <v>45</v>
+      </c>
+      <c r="D36" s="14">
+        <v>150</v>
+      </c>
+      <c r="E36" s="14">
+        <v>20</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>7</v>
+      </c>
+      <c r="H36" s="14">
+        <v>90</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+        <v>385</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B37" s="14">
+        <v>450</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>190</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>200</v>
+      </c>
+      <c r="G37" s="14">
+        <v>4</v>
+      </c>
+      <c r="H37" s="14">
+        <v>180</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011C7138-2E4C-40AC-A5E2-557ED1C0C450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389CB96E-E192-4E3A-B593-9EE703141AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,12 @@
   </si>
   <si>
     <t xml:space="preserve">Excited because today was celebrated fresher party in lpu , so I was enjoy very much. </t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>happy because today declear CA exam result of comminication skill and I got 23/30.</t>
   </si>
 </sst>
 </file>
@@ -2553,48 +2559,96 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46335</v>
+      </c>
+      <c r="B38" s="14">
+        <v>580</v>
+      </c>
+      <c r="C38" s="14">
+        <v>50</v>
+      </c>
+      <c r="D38" s="14">
+        <v>190</v>
+      </c>
+      <c r="E38" s="14">
+        <v>50</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>90</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+        <v>230</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46365</v>
+      </c>
+      <c r="B39" s="14">
+        <v>520</v>
+      </c>
+      <c r="C39" s="14">
+        <v>60</v>
+      </c>
+      <c r="D39" s="14">
+        <v>150</v>
+      </c>
+      <c r="E39" s="14">
+        <v>90</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>190</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389CB96E-E192-4E3A-B593-9EE703141AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B85EC3-BD7A-4A0C-B946-8FF033780987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>happy because today declear CA exam result of comminication skill and I got 23/30.</t>
+  </si>
+  <si>
+    <t>2026-13-09</t>
   </si>
 </sst>
 </file>
@@ -2651,26 +2654,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="14">
+        <v>520</v>
+      </c>
+      <c r="C40" s="14">
+        <v>50</v>
+      </c>
+      <c r="D40" s="14">
+        <v>150</v>
+      </c>
+      <c r="E40" s="14">
+        <v>90</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>190</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B85EC3-BD7A-4A0C-B946-8FF033780987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541EC89E-98D2-4266-B7A6-FCBF7882B6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>2026-13-09</t>
+  </si>
+  <si>
+    <t>2026-14-09</t>
   </si>
 </sst>
 </file>
@@ -2700,26 +2703,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="14">
+        <v>520</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>90</v>
+      </c>
+      <c r="E41" s="14">
+        <v>20</v>
+      </c>
+      <c r="F41" s="14">
+        <v>250</v>
+      </c>
+      <c r="G41" s="14">
+        <v>5</v>
+      </c>
+      <c r="H41" s="14">
+        <v>150</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541EC89E-98D2-4266-B7A6-FCBF7882B6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15D7379-AE80-40BD-A80F-4070BC25E243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,12 @@
   </si>
   <si>
     <t>2026-14-09</t>
+  </si>
+  <si>
+    <t>2026-15-09</t>
+  </si>
+  <si>
+    <t>felling nervous because today had conduct ca exam oF python on mars platfrom and at last my exam gone excelent and result are also declear , so I got 43 out of 50.</t>
   </si>
 </sst>
 </file>
@@ -2748,27 +2754,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+    <row r="42" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="14">
+        <v>520</v>
+      </c>
+      <c r="C42" s="14">
+        <v>50</v>
+      </c>
+      <c r="D42" s="14">
+        <v>20</v>
+      </c>
+      <c r="E42" s="14">
+        <v>50</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>150</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15D7379-AE80-40BD-A80F-4070BC25E243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BCB1A7-9FE0-44D8-9808-5C8B302751D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>felling nervous because today had conduct ca exam oF python on mars platfrom and at last my exam gone excelent and result are also declear , so I got 43 out of 50.</t>
+  </si>
+  <si>
+    <t>2026-16-09</t>
   </si>
 </sst>
 </file>
@@ -2801,26 +2804,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="14">
+        <v>520</v>
+      </c>
+      <c r="C43" s="14">
+        <v>50</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>50</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>150</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BCB1A7-9FE0-44D8-9808-5C8B302751D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A4E11B-B40F-4EB9-B0F9-360FA2B67F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>2026-16-09</t>
+  </si>
+  <si>
+    <t>2026-17-09</t>
   </si>
 </sst>
 </file>
@@ -2850,26 +2853,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="14">
+        <v>520</v>
+      </c>
+      <c r="C44" s="14">
+        <v>20</v>
+      </c>
+      <c r="D44" s="14">
+        <v>60</v>
+      </c>
+      <c r="E44" s="14">
+        <v>30</v>
+      </c>
+      <c r="F44" s="14">
+        <v>200</v>
+      </c>
+      <c r="G44" s="14">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14">
+        <v>160</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A4E11B-B40F-4EB9-B0F9-360FA2B67F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924EBE4B-EDB5-4FA5-8ACF-697B0601EB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>2026-17-09</t>
+  </si>
+  <si>
+    <t>2026-18-09</t>
+  </si>
+  <si>
+    <t>Today I get a minor project in python, I am maintaing this data every day, accourding this data I have to make minnor project I excided for making this project.</t>
   </si>
 </sst>
 </file>
@@ -2898,27 +2904,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+    <row r="45" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A45" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>130</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>130</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924EBE4B-EDB5-4FA5-8ACF-697B0601EB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD83B66-9317-430D-B7A3-61109EABC2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t>Today I get a minor project in python, I am maintaing this data every day, accourding this data I have to make minnor project I excided for making this project.</t>
+  </si>
+  <si>
+    <t>2026-19-09</t>
+  </si>
+  <si>
+    <t>2026-20-09</t>
   </si>
 </sst>
 </file>
@@ -2951,48 +2957,96 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="14">
+        <v>480</v>
+      </c>
+      <c r="C46" s="14">
+        <v>20</v>
+      </c>
+      <c r="D46" s="14">
+        <v>90</v>
+      </c>
+      <c r="E46" s="14">
+        <v>20</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>120</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="14">
+        <v>520</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>120</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD83B66-9317-430D-B7A3-61109EABC2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6774D14-4860-4878-BB4D-D8B5D6A25A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>2026-20-09</t>
+  </si>
+  <si>
+    <t>2026-21-09</t>
   </si>
 </sst>
 </file>
@@ -3049,26 +3052,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="14">
+        <v>410</v>
+      </c>
+      <c r="C48" s="14">
+        <v>50</v>
+      </c>
+      <c r="D48" s="14">
+        <v>90</v>
+      </c>
+      <c r="E48" s="14">
+        <v>50</v>
+      </c>
+      <c r="F48" s="14">
+        <v>250</v>
+      </c>
+      <c r="G48" s="14">
+        <v>5</v>
+      </c>
+      <c r="H48" s="14">
+        <v>190</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6774D14-4860-4878-BB4D-D8B5D6A25A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2944B8-444C-499F-951C-5384DE4FF9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>2026-21-09</t>
+  </si>
+  <si>
+    <t>2026-22-09</t>
   </si>
 </sst>
 </file>
@@ -3098,26 +3101,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" s="14">
+        <v>410</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>20</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>350</v>
+      </c>
+      <c r="G49" s="14">
+        <v>7</v>
+      </c>
+      <c r="H49" s="14">
+        <v>130</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2944B8-444C-499F-951C-5384DE4FF9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B7A440-B795-46E2-8621-BDBDB52E3ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>2026-22-09</t>
+  </si>
+  <si>
+    <t>2026-23-09</t>
   </si>
 </sst>
 </file>
@@ -3147,26 +3150,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="14">
+        <v>480</v>
+      </c>
+      <c r="C50" s="14">
+        <v>20</v>
+      </c>
+      <c r="D50" s="14">
+        <v>120</v>
+      </c>
+      <c r="E50" s="14">
+        <v>30</v>
+      </c>
+      <c r="F50" s="14">
+        <v>300</v>
+      </c>
+      <c r="G50" s="14">
+        <v>6</v>
+      </c>
+      <c r="H50" s="14">
+        <v>120</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B7A440-B795-46E2-8621-BDBDB52E3ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9B14B6-BAE3-4A0B-A552-826995256BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>2026-23-09</t>
+  </si>
+  <si>
+    <t>2026-24-09</t>
   </si>
 </sst>
 </file>
@@ -3196,26 +3199,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="14">
+        <v>520</v>
+      </c>
+      <c r="C51" s="14">
+        <v>50</v>
+      </c>
+      <c r="D51" s="14">
+        <v>120</v>
+      </c>
+      <c r="E51" s="14">
+        <v>50</v>
+      </c>
+      <c r="F51" s="14">
+        <v>150</v>
+      </c>
+      <c r="G51" s="14">
+        <v>3</v>
+      </c>
+      <c r="H51" s="14">
+        <v>150</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9B14B6-BAE3-4A0B-A552-826995256BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFFAACE-CB43-4309-941F-45A0C6545151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>2026-24-09</t>
+  </si>
+  <si>
+    <t>2026-25-09</t>
   </si>
 </sst>
 </file>
@@ -3245,26 +3248,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="14">
+        <v>520</v>
+      </c>
+      <c r="C52" s="14">
+        <v>60</v>
+      </c>
+      <c r="D52" s="14">
+        <v>190</v>
+      </c>
+      <c r="E52" s="14">
+        <v>20</v>
+      </c>
+      <c r="F52" s="14">
+        <v>250</v>
+      </c>
+      <c r="G52" s="14">
+        <v>5</v>
+      </c>
+      <c r="H52" s="14">
+        <v>120</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFFAACE-CB43-4309-941F-45A0C6545151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6B7820-A009-4EA9-A626-B956A61056DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,39 @@
   </si>
   <si>
     <t>2026-25-09</t>
+  </si>
+  <si>
+    <t>2026-26-09</t>
+  </si>
+  <si>
+    <t>2026-27-09</t>
+  </si>
+  <si>
+    <t>Today we are so scared because some false or wrong infromation, there was a lot of confusion and disturbance at our university. So, for safety of the student,  the university gave us a 10-days holiday.</t>
+  </si>
+  <si>
+    <t>2026-28-09</t>
+  </si>
+  <si>
+    <t>Today I am going home. It will take around two days to reach, and I am already on the train.</t>
+  </si>
+  <si>
+    <t>2026-29-09</t>
+  </si>
+  <si>
+    <t>Travelling in train.</t>
+  </si>
+  <si>
+    <t>2026-30-09</t>
+  </si>
+  <si>
+    <t>I am so tired. And I heart a news that every thing is normal in lpu and from 5/10/2026 will going online classes.</t>
+  </si>
+  <si>
+    <t>Something issue my github profile that why my data cannot upload in github.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I Am fixing my github issue from chatgpt. </t>
   </si>
 </sst>
 </file>
@@ -3293,137 +3326,281 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+    <row r="53" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" s="14">
+        <v>520</v>
+      </c>
+      <c r="C53" s="14">
+        <v>50</v>
+      </c>
+      <c r="D53" s="14">
+        <v>150</v>
+      </c>
+      <c r="E53" s="14">
+        <v>60</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>190</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="14">
+        <v>480</v>
+      </c>
+      <c r="C54" s="14">
+        <v>60</v>
+      </c>
+      <c r="D54" s="14">
+        <v>120</v>
+      </c>
+      <c r="E54" s="14">
+        <v>90</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>120</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" s="14">
+        <v>560</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>90</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>650</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>790</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" s="14">
+        <v>590</v>
+      </c>
+      <c r="C56" s="14">
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <v>0</v>
+      </c>
+      <c r="E56" s="14">
+        <v>0</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>120</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>710</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" s="14">
+        <v>590</v>
+      </c>
+      <c r="C57" s="14">
+        <v>0</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>160</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="13">
+        <v>46032</v>
+      </c>
+      <c r="B58" s="14">
+        <v>460</v>
+      </c>
+      <c r="C58" s="14">
+        <v>0</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>220</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6B7820-A009-4EA9-A626-B956A61056DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158DE8A4-6754-4576-B74E-007D94D56A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3603,26 +3603,50 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46063</v>
+      </c>
+      <c r="B59" s="14">
+        <v>550</v>
+      </c>
+      <c r="C59" s="14">
+        <v>0</v>
+      </c>
+      <c r="D59" s="14">
+        <v>0</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>250</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158DE8A4-6754-4576-B74E-007D94D56A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D9998F-E708-4E49-8462-45C4ED7C1800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3649,26 +3649,50 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46091</v>
+      </c>
+      <c r="B60" s="14">
+        <v>450</v>
+      </c>
+      <c r="C60" s="14">
+        <v>0</v>
+      </c>
+      <c r="D60" s="14">
+        <v>0</v>
+      </c>
+      <c r="E60" s="14">
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>350</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D9998F-E708-4E49-8462-45C4ED7C1800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447F469D-672C-45C5-9874-255F919A74B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3695,26 +3695,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46122</v>
+      </c>
+      <c r="B61" s="14">
+        <v>460</v>
+      </c>
+      <c r="C61" s="14">
+        <v>0</v>
+      </c>
+      <c r="D61" s="14">
+        <v>90</v>
+      </c>
+      <c r="E61" s="14">
+        <v>60</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>320</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447F469D-672C-45C5-9874-255F919A74B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FD90D8-A0F1-41F4-8035-FC3ECAB00954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t xml:space="preserve">Today I Am fixing my github issue from chatgpt. </t>
+  </si>
+  <si>
+    <t>today was conduct online classes.</t>
   </si>
 </sst>
 </file>
@@ -3740,27 +3743,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+    <row r="62" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="13">
+        <v>46152</v>
+      </c>
+      <c r="B62" s="14">
+        <v>520</v>
+      </c>
+      <c r="C62" s="14">
+        <v>20</v>
+      </c>
+      <c r="D62" s="14">
+        <v>60</v>
+      </c>
+      <c r="E62" s="14">
+        <v>40</v>
+      </c>
+      <c r="F62" s="14">
+        <v>250</v>
+      </c>
+      <c r="G62" s="14">
+        <v>5</v>
+      </c>
+      <c r="H62" s="14">
+        <v>350</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FD90D8-A0F1-41F4-8035-FC3ECAB00954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AE2B32-A6C7-41B0-959D-C6E34F6226C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3790,26 +3790,50 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46183</v>
+      </c>
+      <c r="B63" s="14">
+        <v>540</v>
+      </c>
+      <c r="C63" s="14">
+        <v>30</v>
+      </c>
+      <c r="D63" s="14">
+        <v>90</v>
+      </c>
+      <c r="E63" s="14">
+        <v>40</v>
+      </c>
+      <c r="F63" s="14">
+        <v>350</v>
+      </c>
+      <c r="G63" s="14">
+        <v>7</v>
+      </c>
+      <c r="H63" s="14">
+        <v>350</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AE2B32-A6C7-41B0-959D-C6E34F6226C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93810E9-C48E-46D5-AFB7-2C742C8C7CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3836,26 +3836,50 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46213</v>
+      </c>
+      <c r="B64" s="14">
+        <v>320</v>
+      </c>
+      <c r="C64" s="14">
+        <v>30</v>
+      </c>
+      <c r="D64" s="14">
+        <v>120</v>
+      </c>
+      <c r="E64" s="14">
+        <v>20</v>
+      </c>
+      <c r="F64" s="14">
+        <v>300</v>
+      </c>
+      <c r="G64" s="14">
+        <v>6</v>
+      </c>
+      <c r="H64" s="14">
+        <v>250</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93810E9-C48E-46D5-AFB7-2C742C8C7CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F61E66E-49D1-4AF9-949B-3DB070B9375D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3882,26 +3882,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46244</v>
+      </c>
+      <c r="B65" s="14">
+        <v>180</v>
+      </c>
+      <c r="C65" s="14">
+        <v>60</v>
+      </c>
+      <c r="D65" s="14">
+        <v>120</v>
+      </c>
+      <c r="E65" s="14">
+        <v>60</v>
+      </c>
+      <c r="F65" s="14">
+        <v>200</v>
+      </c>
+      <c r="G65" s="14">
+        <v>4</v>
+      </c>
+      <c r="H65" s="14">
+        <v>230</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F23FAA3-CF63-40F5-BDF4-E137EDCE1582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4A24FD-9F35-43B2-B8CF-5391B06F77B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -546,12 +546,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1035,74 +1035,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <v>12626818</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1149,7 +1149,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
+      <c r="A6" s="13">
         <v>46303</v>
       </c>
       <c r="B6" s="9">
@@ -1195,7 +1195,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="16">
+      <c r="A7" s="13">
         <v>46334</v>
       </c>
       <c r="B7" s="9">
@@ -1241,7 +1241,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="16">
+      <c r="A8" s="13">
         <v>46364</v>
       </c>
       <c r="B8" s="9">
@@ -1287,7 +1287,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
         <v>57</v>
       </c>
       <c r="B9" s="9">
@@ -1333,7 +1333,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="13" t="s">
         <v>58</v>
       </c>
       <c r="B10" s="9">
@@ -1379,7 +1379,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="13" t="s">
         <v>115</v>
       </c>
       <c r="B11" s="9">
@@ -1425,7 +1425,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B12" s="9">
@@ -1471,7 +1471,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="13" t="s">
         <v>67</v>
       </c>
       <c r="B13" s="9">
@@ -1517,7 +1517,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="13" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="9">
@@ -1563,7 +1563,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B15" s="9">
@@ -1609,7 +1609,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="13" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="9">
@@ -1655,7 +1655,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="13" t="s">
         <v>71</v>
       </c>
       <c r="B17" s="9">
@@ -1701,7 +1701,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="13" t="s">
         <v>72</v>
       </c>
       <c r="B18" s="9">
@@ -1747,7 +1747,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="13" t="s">
         <v>73</v>
       </c>
       <c r="B19" s="9">
@@ -1793,7 +1793,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="13" t="s">
         <v>74</v>
       </c>
       <c r="B20" s="9">
@@ -1839,7 +1839,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="13" t="s">
         <v>75</v>
       </c>
       <c r="B21" s="9">
@@ -1885,7 +1885,7 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="13" t="s">
         <v>76</v>
       </c>
       <c r="B22" s="9">
@@ -1931,7 +1931,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="13" t="s">
         <v>77</v>
       </c>
       <c r="B23" s="9">
@@ -1977,7 +1977,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="13" t="s">
         <v>78</v>
       </c>
       <c r="B24" s="9">
@@ -2023,7 +2023,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="13" t="s">
         <v>79</v>
       </c>
       <c r="B25" s="9">
@@ -2069,7 +2069,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B26" s="9">
@@ -2115,7 +2115,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="13" t="s">
         <v>81</v>
       </c>
       <c r="B27" s="9">
@@ -2161,7 +2161,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="16">
+      <c r="A28" s="13">
         <v>46031</v>
       </c>
       <c r="B28" s="9">
@@ -2207,7 +2207,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="16">
+      <c r="A29" s="13">
         <v>46062</v>
       </c>
       <c r="B29" s="9">
@@ -2253,7 +2253,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="16">
+      <c r="A30" s="13">
         <v>46090</v>
       </c>
       <c r="B30" s="9">
@@ -2299,7 +2299,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="16">
+      <c r="A31" s="13">
         <v>46121</v>
       </c>
       <c r="B31" s="9">
@@ -2345,7 +2345,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="16">
+      <c r="A32" s="13">
         <v>46151</v>
       </c>
       <c r="B32" s="9">
@@ -2391,7 +2391,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="16">
+      <c r="A33" s="13">
         <v>46182</v>
       </c>
       <c r="B33" s="9">
@@ -2437,7 +2437,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="16">
+      <c r="A34" s="13">
         <v>46212</v>
       </c>
       <c r="B34" s="9">
@@ -2483,7 +2483,7 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="16">
+      <c r="A35" s="13">
         <v>46243</v>
       </c>
       <c r="B35" s="9">
@@ -2529,7 +2529,7 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="16">
+      <c r="A36" s="13">
         <v>46274</v>
       </c>
       <c r="B36" s="9">
@@ -2575,7 +2575,7 @@
       </c>
     </row>
     <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="16">
+      <c r="A37" s="13">
         <v>46304</v>
       </c>
       <c r="B37" s="9">
@@ -2621,7 +2621,7 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="16">
+      <c r="A38" s="13">
         <v>46335</v>
       </c>
       <c r="B38" s="9">
@@ -2667,7 +2667,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="16">
+      <c r="A39" s="13">
         <v>46365</v>
       </c>
       <c r="B39" s="9">
@@ -2713,7 +2713,7 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="13" t="s">
         <v>88</v>
       </c>
       <c r="B40" s="9">
@@ -2759,7 +2759,7 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B41" s="9">
@@ -2805,7 +2805,7 @@
       </c>
     </row>
     <row r="42" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B42" s="9">
@@ -2851,7 +2851,7 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="13" t="s">
         <v>92</v>
       </c>
       <c r="B43" s="9">
@@ -2897,7 +2897,7 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="13" t="s">
         <v>93</v>
       </c>
       <c r="B44" s="9">
@@ -2943,7 +2943,7 @@
       </c>
     </row>
     <row r="45" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="13" t="s">
         <v>94</v>
       </c>
       <c r="B45" s="9">
@@ -2989,7 +2989,7 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="13" t="s">
         <v>96</v>
       </c>
       <c r="B46" s="9">
@@ -3035,7 +3035,7 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="13" t="s">
         <v>97</v>
       </c>
       <c r="B47" s="9">
@@ -3081,7 +3081,7 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="13" t="s">
         <v>98</v>
       </c>
       <c r="B48" s="9">
@@ -3127,7 +3127,7 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="13" t="s">
         <v>99</v>
       </c>
       <c r="B49" s="9">
@@ -3173,7 +3173,7 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="13" t="s">
         <v>100</v>
       </c>
       <c r="B50" s="9">
@@ -3219,7 +3219,7 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="13" t="s">
         <v>101</v>
       </c>
       <c r="B51" s="9">
@@ -3265,7 +3265,7 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="13" t="s">
         <v>102</v>
       </c>
       <c r="B52" s="9">
@@ -3311,7 +3311,7 @@
       </c>
     </row>
     <row r="53" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B53" s="9">
@@ -3357,7 +3357,7 @@
       </c>
     </row>
     <row r="54" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="13" t="s">
         <v>104</v>
       </c>
       <c r="B54" s="9">
@@ -3403,7 +3403,7 @@
       </c>
     </row>
     <row r="55" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="13" t="s">
         <v>106</v>
       </c>
       <c r="B55" s="9">
@@ -3449,7 +3449,7 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="13" t="s">
         <v>108</v>
       </c>
       <c r="B56" s="9">
@@ -3495,7 +3495,7 @@
       </c>
     </row>
     <row r="57" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="13" t="s">
         <v>110</v>
       </c>
       <c r="B57" s="9">
@@ -3541,7 +3541,7 @@
       </c>
     </row>
     <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="16">
+      <c r="A58" s="13">
         <v>46032</v>
       </c>
       <c r="B58" s="9">
@@ -3587,7 +3587,7 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="16">
+      <c r="A59" s="13">
         <v>46063</v>
       </c>
       <c r="B59" s="9">
@@ -3633,7 +3633,7 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="16">
+      <c r="A60" s="13">
         <v>46091</v>
       </c>
       <c r="B60" s="9">
@@ -3679,7 +3679,7 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="16">
+      <c r="A61" s="13">
         <v>46122</v>
       </c>
       <c r="B61" s="9">
@@ -3725,7 +3725,7 @@
       </c>
     </row>
     <row r="62" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="16">
+      <c r="A62" s="13">
         <v>46152</v>
       </c>
       <c r="B62" s="9">
@@ -3771,7 +3771,7 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="16">
+      <c r="A63" s="13">
         <v>46183</v>
       </c>
       <c r="B63" s="9">
@@ -3817,7 +3817,7 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="16">
+      <c r="A64" s="13">
         <v>46213</v>
       </c>
       <c r="B64" s="9">
@@ -3863,7 +3863,7 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="16">
+      <c r="A65" s="13">
         <v>46244</v>
       </c>
       <c r="B65" s="9">
@@ -3909,7 +3909,7 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="16">
+      <c r="A66" s="13">
         <v>46275</v>
       </c>
       <c r="B66" s="9">
@@ -3955,7 +3955,7 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="16">
+      <c r="A67" s="13">
         <v>46305</v>
       </c>
       <c r="B67" s="9">
@@ -4001,26 +4001,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
+      <c r="A68" s="13">
+        <v>46336</v>
+      </c>
+      <c r="B68" s="9">
+        <v>350</v>
+      </c>
+      <c r="C68" s="9">
+        <v>0</v>
+      </c>
+      <c r="D68" s="9">
+        <v>60</v>
+      </c>
+      <c r="E68" s="9">
+        <v>20</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0</v>
+      </c>
+      <c r="G68" s="9">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
+        <v>360</v>
+      </c>
+      <c r="I68" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
+        <v>790</v>
+      </c>
+      <c r="J68" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="12"/>
+        <v>650</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4A24FD-9F35-43B2-B8CF-5391B06F77B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F199FA5C-7A33-4D26-ADDA-AF4C1B8860A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4047,26 +4047,50 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
+      <c r="A69" s="13">
+        <v>46367</v>
+      </c>
+      <c r="B69" s="9">
+        <v>460</v>
+      </c>
+      <c r="C69" s="9">
+        <v>60</v>
+      </c>
+      <c r="D69" s="9">
+        <v>120</v>
+      </c>
+      <c r="E69" s="9">
+        <v>60</v>
+      </c>
+      <c r="F69" s="9">
+        <v>0</v>
+      </c>
+      <c r="G69" s="9">
+        <v>0</v>
+      </c>
+      <c r="H69" s="9">
+        <v>360</v>
+      </c>
+      <c r="I69" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J69" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="12"/>
+        <v>380</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N69" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F199FA5C-7A33-4D26-ADDA-AF4C1B8860A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2BCA2B-8F20-4E6B-881C-B8A7D10D7FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="117">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -383,6 +383,9 @@
   </si>
   <si>
     <t>15/08/2026</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4048,7 +4051,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="13">
-        <v>46367</v>
+        <v>46366</v>
       </c>
       <c r="B69" s="9">
         <v>460</v>
@@ -4093,26 +4096,50 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
+      <c r="A70" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B70" s="9">
+        <v>360</v>
+      </c>
+      <c r="C70" s="9">
+        <v>20</v>
+      </c>
+      <c r="D70" s="9">
+        <v>120</v>
+      </c>
+      <c r="E70" s="9">
+        <v>60</v>
+      </c>
+      <c r="F70" s="9">
+        <v>0</v>
+      </c>
+      <c r="G70" s="9">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
+        <v>250</v>
+      </c>
+      <c r="I70" s="10">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
+        <v>810</v>
+      </c>
+      <c r="J70" s="10">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="12"/>
+        <v>630</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N70" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2BCA2B-8F20-4E6B-881C-B8A7D10D7FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B632FF5-209C-43FB-8C5A-D950BDB0E2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4142,26 +4145,50 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
+      <c r="A71" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B71" s="9">
+        <v>420</v>
+      </c>
+      <c r="C71" s="9">
+        <v>30</v>
+      </c>
+      <c r="D71" s="9">
+        <v>220</v>
+      </c>
+      <c r="E71" s="9">
+        <v>30</v>
+      </c>
+      <c r="F71" s="9">
+        <v>0</v>
+      </c>
+      <c r="G71" s="9">
+        <v>0</v>
+      </c>
+      <c r="H71" s="9">
+        <v>320</v>
+      </c>
+      <c r="I71" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J71" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="12"/>
+        <v>420</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N71" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B632FF5-209C-43FB-8C5A-D950BDB0E2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E655DB95-6D27-427A-AFB6-C92CC9517A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="119">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,6 +389,9 @@
   </si>
   <si>
     <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4191,26 +4194,50 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
+      <c r="A72" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B72" s="9">
+        <v>350</v>
+      </c>
+      <c r="C72" s="9">
+        <v>60</v>
+      </c>
+      <c r="D72" s="9">
+        <v>120</v>
+      </c>
+      <c r="E72" s="9">
+        <v>120</v>
+      </c>
+      <c r="F72" s="9">
+        <v>0</v>
+      </c>
+      <c r="G72" s="9">
+        <v>0</v>
+      </c>
+      <c r="H72" s="9">
+        <v>230</v>
+      </c>
+      <c r="I72" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+        <v>880</v>
+      </c>
+      <c r="J72" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="12"/>
+        <v>560</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E655DB95-6D27-427A-AFB6-C92CC9517A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0E6550-CEE9-498B-9FDD-CC2B2D860372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="121">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -392,6 +392,12 @@
   </si>
   <si>
     <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>I am in the train. I am going to return punjab</t>
   </si>
 </sst>
 </file>
@@ -4239,27 +4245,51 @@
         <v>65</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
+    <row r="73" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B73" s="9">
+        <v>540</v>
+      </c>
+      <c r="C73" s="9">
+        <v>50</v>
+      </c>
+      <c r="D73" s="9">
+        <v>60</v>
+      </c>
+      <c r="E73" s="9">
+        <v>60</v>
+      </c>
+      <c r="F73" s="9">
+        <v>0</v>
+      </c>
+      <c r="G73" s="9">
+        <v>0</v>
+      </c>
+      <c r="H73" s="9">
+        <v>360</v>
+      </c>
+      <c r="I73" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J73" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="12"/>
+        <v>370</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0E6550-CEE9-498B-9FDD-CC2B2D860372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DB6194-D4FF-41D1-AC04-6A6AA405CCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="122">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>I am in the train. I am going to return punjab</t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4292,26 +4295,50 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
+      <c r="A74" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B74" s="9">
+        <v>350</v>
+      </c>
+      <c r="C74" s="9">
+        <v>60</v>
+      </c>
+      <c r="D74" s="9">
+        <v>30</v>
+      </c>
+      <c r="E74" s="9">
+        <v>30</v>
+      </c>
+      <c r="F74" s="9">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9">
+        <v>350</v>
+      </c>
+      <c r="I74" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+        <v>820</v>
+      </c>
+      <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="12"/>
+        <v>620</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N74" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DB6194-D4FF-41D1-AC04-6A6AA405CCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3693A9-3213-43CD-AC36-AF7E560F6CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="123">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>18/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4341,26 +4344,50 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
+      <c r="A75" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" s="9">
+        <v>480</v>
+      </c>
+      <c r="C75" s="9">
+        <v>0</v>
+      </c>
+      <c r="D75" s="9">
+        <v>0</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0</v>
+      </c>
+      <c r="F75" s="9">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>320</v>
+      </c>
+      <c r="I75" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+        <v>800</v>
+      </c>
+      <c r="J75" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="12"/>
+        <v>640</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3693A9-3213-43CD-AC36-AF7E560F6CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7183D771-DC49-4F45-B035-84B4931E3689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="124">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>18/10/2026</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4390,26 +4393,50 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
+      <c r="A76" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B76" s="9">
+        <v>350</v>
+      </c>
+      <c r="C76" s="9">
+        <v>20</v>
+      </c>
+      <c r="D76" s="9">
+        <v>120</v>
+      </c>
+      <c r="E76" s="9">
+        <v>20</v>
+      </c>
+      <c r="F76" s="9">
+        <v>150</v>
+      </c>
+      <c r="G76" s="9">
+        <v>3</v>
+      </c>
+      <c r="H76" s="9">
+        <v>120</v>
+      </c>
+      <c r="I76" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
+        <v>780</v>
+      </c>
+      <c r="J76" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="12"/>
+        <v>660</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N76" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7183D771-DC49-4F45-B035-84B4931E3689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB27F8CD-672F-407B-9BD9-EFC36BEB5C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="125">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -407,6 +407,9 @@
   </si>
   <si>
     <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4439,26 +4442,50 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
+      <c r="A77" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" s="9">
+        <v>360</v>
+      </c>
+      <c r="C77" s="9">
+        <v>30</v>
+      </c>
+      <c r="D77" s="9">
+        <v>60</v>
+      </c>
+      <c r="E77" s="9">
+        <v>30</v>
+      </c>
+      <c r="F77" s="9">
+        <v>0</v>
+      </c>
+      <c r="G77" s="9">
+        <v>0</v>
+      </c>
+      <c r="H77" s="9">
+        <v>250</v>
+      </c>
+      <c r="I77" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
+        <v>730</v>
+      </c>
+      <c r="J77" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="12"/>
+        <v>710</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N77" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB27F8CD-672F-407B-9BD9-EFC36BEB5C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA64F2B5-874E-452D-A2D4-DB20A06DADF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="126">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -410,6 +410,9 @@
   </si>
   <si>
     <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>21/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4488,26 +4491,50 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
+      <c r="A78" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" s="9">
+        <v>480</v>
+      </c>
+      <c r="C78" s="9">
+        <v>20</v>
+      </c>
+      <c r="D78" s="9">
+        <v>120</v>
+      </c>
+      <c r="E78" s="9">
+        <v>30</v>
+      </c>
+      <c r="F78" s="9">
+        <v>300</v>
+      </c>
+      <c r="G78" s="9">
+        <v>6</v>
+      </c>
+      <c r="H78" s="9">
+        <v>360</v>
+      </c>
+      <c r="I78" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J78" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="12"/>
+        <v>130</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA64F2B5-874E-452D-A2D4-DB20A06DADF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1146EC8-3FF9-4AB0-BED5-7DAF70A12671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="127">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -413,6 +413,9 @@
   </si>
   <si>
     <t>21/10/2026</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4537,26 +4540,50 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
+      <c r="A79" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79" s="9">
+        <v>360</v>
+      </c>
+      <c r="C79" s="9">
+        <v>30</v>
+      </c>
+      <c r="D79" s="9">
+        <v>60</v>
+      </c>
+      <c r="E79" s="9">
+        <v>30</v>
+      </c>
+      <c r="F79" s="9">
+        <v>200</v>
+      </c>
+      <c r="G79" s="9">
+        <v>4</v>
+      </c>
+      <c r="H79" s="9">
+        <v>360</v>
+      </c>
+      <c r="I79" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J79" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N79" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1146EC8-3FF9-4AB0-BED5-7DAF70A12671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5503E7DA-E7EE-4431-98FF-468F43C9ECB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="128">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -416,6 +416,9 @@
   </si>
   <si>
     <t>22/10/2026</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4586,26 +4589,50 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="10" t="str">
+      <c r="A80" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B80" s="9">
+        <v>420</v>
+      </c>
+      <c r="C80" s="9">
+        <v>60</v>
+      </c>
+      <c r="D80" s="9">
+        <v>30</v>
+      </c>
+      <c r="E80" s="9">
+        <v>60</v>
+      </c>
+      <c r="F80" s="9">
+        <v>150</v>
+      </c>
+      <c r="G80" s="9">
+        <v>3</v>
+      </c>
+      <c r="H80" s="9">
+        <v>420</v>
+      </c>
+      <c r="I80" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="10" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J80" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="12"/>
+        <v>300</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N80" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5503E7DA-E7EE-4431-98FF-468F43C9ECB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3185D7-D451-4BFD-973C-08548C692345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="129">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -419,6 +419,9 @@
   </si>
   <si>
     <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>24/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4635,26 +4638,50 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="10" t="str">
+      <c r="A81" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B81" s="9">
+        <v>420</v>
+      </c>
+      <c r="C81" s="9">
+        <v>40</v>
+      </c>
+      <c r="D81" s="9">
+        <v>30</v>
+      </c>
+      <c r="E81" s="9">
+        <v>50</v>
+      </c>
+      <c r="F81" s="9">
+        <v>0</v>
+      </c>
+      <c r="G81" s="9">
+        <v>0</v>
+      </c>
+      <c r="H81" s="9">
+        <v>360</v>
+      </c>
+      <c r="I81" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="10" t="str">
+        <v>900</v>
+      </c>
+      <c r="J81" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="11"/>
-      <c r="N81" s="12"/>
+        <v>540</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N81" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3185D7-D451-4BFD-973C-08548C692345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B315CE75-3FEC-4120-82A7-7CE8819AB98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="130">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -422,6 +422,9 @@
   </si>
   <si>
     <t>24/10/2026</t>
+  </si>
+  <si>
+    <t>25/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4684,26 +4687,50 @@
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="8"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="10" t="str">
+      <c r="A82" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B82" s="9">
+        <v>360</v>
+      </c>
+      <c r="C82" s="9">
+        <v>30</v>
+      </c>
+      <c r="D82" s="9">
+        <v>60</v>
+      </c>
+      <c r="E82" s="9">
+        <v>20</v>
+      </c>
+      <c r="F82" s="9">
+        <v>0</v>
+      </c>
+      <c r="G82" s="9">
+        <v>0</v>
+      </c>
+      <c r="H82" s="9">
+        <v>420</v>
+      </c>
+      <c r="I82" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="10" t="str">
+        <v>890</v>
+      </c>
+      <c r="J82" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="11"/>
-      <c r="L82" s="11"/>
-      <c r="M82" s="11"/>
-      <c r="N82" s="12"/>
+        <v>550</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L82" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M82" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N82" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B315CE75-3FEC-4120-82A7-7CE8819AB98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FC4902-3862-452E-8B9D-D9C9BAFCDFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="131">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -425,6 +425,9 @@
   </si>
   <si>
     <t>25/10/2026</t>
+  </si>
+  <si>
+    <t>26/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4733,26 +4736,50 @@
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="8"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="10" t="str">
+      <c r="A83" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B83" s="9">
+        <v>460</v>
+      </c>
+      <c r="C83" s="9">
+        <v>30</v>
+      </c>
+      <c r="D83" s="9">
+        <v>60</v>
+      </c>
+      <c r="E83" s="9">
+        <v>30</v>
+      </c>
+      <c r="F83" s="9">
+        <v>0</v>
+      </c>
+      <c r="G83" s="9">
+        <v>0</v>
+      </c>
+      <c r="H83" s="9">
+        <v>360</v>
+      </c>
+      <c r="I83" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="10" t="str">
+        <v>940</v>
+      </c>
+      <c r="J83" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="11"/>
-      <c r="L83" s="11"/>
-      <c r="M83" s="11"/>
-      <c r="N83" s="12"/>
+        <v>500</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N83" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FC4902-3862-452E-8B9D-D9C9BAFCDFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3868593-EB8F-4A48-9357-88D4D2365568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="132">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -428,6 +428,9 @@
   </si>
   <si>
     <t>26/10/2026</t>
+  </si>
+  <si>
+    <t>27/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4782,26 +4785,50 @@
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" s="8"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="10" t="str">
+      <c r="A84" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B84" s="9">
+        <v>350</v>
+      </c>
+      <c r="C84" s="9">
+        <v>50</v>
+      </c>
+      <c r="D84" s="9">
+        <v>120</v>
+      </c>
+      <c r="E84" s="9">
+        <v>20</v>
+      </c>
+      <c r="F84" s="9">
+        <v>350</v>
+      </c>
+      <c r="G84" s="9">
+        <v>7</v>
+      </c>
+      <c r="H84" s="9">
+        <v>420</v>
+      </c>
+      <c r="I84" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="10" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J84" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="11"/>
-      <c r="L84" s="11"/>
-      <c r="M84" s="11"/>
-      <c r="N84" s="12"/>
+        <v>130</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L84" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M84" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N84" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3868593-EB8F-4A48-9357-88D4D2365568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F36842E-8934-4B75-8C83-526120E67A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="133">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -431,6 +431,9 @@
   </si>
   <si>
     <t>27/10/2026</t>
+  </si>
+  <si>
+    <t>28/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4831,26 +4834,50 @@
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" s="8"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="10" t="str">
+      <c r="A85" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B85" s="9">
+        <v>420</v>
+      </c>
+      <c r="C85" s="9">
+        <v>60</v>
+      </c>
+      <c r="D85" s="9">
+        <v>60</v>
+      </c>
+      <c r="E85" s="9">
+        <v>30</v>
+      </c>
+      <c r="F85" s="9">
+        <v>300</v>
+      </c>
+      <c r="G85" s="9">
+        <v>6</v>
+      </c>
+      <c r="H85" s="9">
+        <v>230</v>
+      </c>
+      <c r="I85" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="10" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J85" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="11"/>
-      <c r="L85" s="11"/>
-      <c r="M85" s="11"/>
-      <c r="N85" s="12"/>
+        <v>340</v>
+      </c>
+      <c r="K85" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L85" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M85" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N85" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F36842E-8934-4B75-8C83-526120E67A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6B614A-63E5-4B3E-892F-E5022078B8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="134">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -434,6 +434,9 @@
   </si>
   <si>
     <t>28/10/2026</t>
+  </si>
+  <si>
+    <t>29/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4880,26 +4883,50 @@
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86" s="8"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
-      <c r="I86" s="10" t="str">
+      <c r="A86" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B86" s="9">
+        <v>360</v>
+      </c>
+      <c r="C86" s="9">
+        <v>30</v>
+      </c>
+      <c r="D86" s="9">
+        <v>30</v>
+      </c>
+      <c r="E86" s="9">
+        <v>60</v>
+      </c>
+      <c r="F86" s="9">
+        <v>200</v>
+      </c>
+      <c r="G86" s="9">
+        <v>4</v>
+      </c>
+      <c r="H86" s="9">
+        <v>360</v>
+      </c>
+      <c r="I86" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J86" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K86" s="11"/>
-      <c r="L86" s="11"/>
-      <c r="M86" s="11"/>
-      <c r="N86" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L86" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M86" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N86" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="8"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\CAP776-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6B614A-63E5-4B3E-892F-E5022078B8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254C163F-8E53-475A-B518-A6270695CEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="135">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -437,6 +437,9 @@
   </si>
   <si>
     <t>29/10/2026</t>
+  </si>
+  <si>
+    <t>30/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4929,26 +4932,50 @@
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87" s="8"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="10" t="str">
+      <c r="A87" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B87" s="9">
+        <v>420</v>
+      </c>
+      <c r="C87" s="9">
+        <v>60</v>
+      </c>
+      <c r="D87" s="9">
+        <v>30</v>
+      </c>
+      <c r="E87" s="9">
+        <v>60</v>
+      </c>
+      <c r="F87" s="9">
+        <v>250</v>
+      </c>
+      <c r="G87" s="9">
+        <v>5</v>
+      </c>
+      <c r="H87" s="9">
+        <v>420</v>
+      </c>
+      <c r="I87" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J87" s="10" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J87" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K87" s="11"/>
-      <c r="L87" s="11"/>
-      <c r="M87" s="11"/>
-      <c r="N87" s="12"/>
+        <v>200</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L87" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M87" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N87" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="8"/>
